--- a/employers_master.xlsx
+++ b/employers_master.xlsx
@@ -721,13 +721,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -834,13 +832,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -903,7 +899,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Monster | Learn4Good</t>
+          <t xml:space="preserve"> | </t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -952,13 +948,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1048,13 +1042,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1146,13 +1138,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1239,13 +1229,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1303,7 +1291,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Talents By Vaia | SWE Career Center - Society Of Women Engineers | JobLeads</t>
+          <t xml:space="preserve"> |  |  | </t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1352,13 +1340,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1421,7 +1407,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -1485,7 +1471,6 @@
           <t>Unclear</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1572,13 +1557,11 @@
           <t>Detroit</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1641,7 +1624,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1775,7 +1758,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1943,13 +1926,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2039,13 +2020,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2108,7 +2087,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W15" t="n">
@@ -2230,11 +2209,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -2286,13 +2261,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2346,11 +2319,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Learn4Good</t>
-        </is>
-      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -2402,13 +2371,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2513,13 +2480,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2573,11 +2538,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>ZipRecruiter</t>
-        </is>
-      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -2624,13 +2585,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2722,13 +2681,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2782,11 +2739,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Talent.com</t>
-        </is>
-      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -2838,13 +2791,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2902,7 +2853,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>ZipRecruiter</t>
+          <t xml:space="preserve"> | </t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2951,13 +2902,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3047,13 +2996,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3101,7 +3048,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Learn4Good | Talent.com | JobLeads</t>
+          <t xml:space="preserve"> |  | </t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3155,13 +3102,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3219,7 +3164,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -3335,7 +3280,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Glassdoor | BeBee</t>
+          <t xml:space="preserve"> | </t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3384,13 +3329,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3441,7 +3384,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t xml:space="preserve"> |  |  |  |  | </t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3495,13 +3438,11 @@
           <t>Detroit</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3583,13 +3524,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3671,13 +3610,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3759,13 +3696,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3845,13 +3780,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3909,7 +3842,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -4062,13 +3995,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4140,13 +4071,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4223,13 +4152,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4277,7 +4204,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>LinkedIn | SalesJobs.com | JobLeads | Tradesmen International | Indeed</t>
+          <t xml:space="preserve"> |  |  |  |  |  |  |  |  | </t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4326,13 +4253,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4409,13 +4334,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4482,13 +4405,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
         <is>
           <t>No listings</t>
         </is>
       </c>
-      <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4546,7 +4467,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4677,7 +4598,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4803,7 +4724,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Indeed | Talents By Vaia</t>
+          <t xml:space="preserve"> |  |  |  |  |  |  | </t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4857,13 +4778,11 @@
           <t>Outside the area</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4921,7 +4840,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5045,11 +4964,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -5101,13 +5016,11 @@
           <t>Outside the area</t>
         </is>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5165,7 +5078,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5296,7 +5209,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5427,7 +5340,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5496,7 +5409,6 @@
           <t>College degree</t>
         </is>
       </c>
-      <c r="AJ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5554,7 +5466,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5623,7 +5535,6 @@
           <t>College degree</t>
         </is>
       </c>
-      <c r="AJ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5681,7 +5592,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5805,11 +5716,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -5861,13 +5768,11 @@
           <t>Around Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5925,7 +5830,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -6056,7 +5961,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -6182,7 +6087,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Cleveland-Cliffs Careers | JobLeads | LinkedIn | Talents By Vaia</t>
+          <t xml:space="preserve"> |  |  |  |  |  |  |  | </t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6236,13 +6141,11 @@
           <t>Detroit</t>
         </is>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6293,11 +6196,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Talents By Vaia</t>
-        </is>
-      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -6349,13 +6248,11 @@
           <t>Detroit</t>
         </is>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6413,7 +6310,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6544,7 +6441,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6613,7 +6510,6 @@
           <t>Training or certificate</t>
         </is>
       </c>
-      <c r="AJ55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6671,7 +6567,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6802,7 +6698,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6933,7 +6829,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -7064,7 +6960,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -7195,7 +7091,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -7264,7 +7160,6 @@
           <t>Training or certificate</t>
         </is>
       </c>
-      <c r="AJ60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7322,7 +7217,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -7453,7 +7348,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7584,7 +7479,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -7715,7 +7610,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7846,7 +7741,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7977,7 +7872,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -8108,7 +8003,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -8239,7 +8134,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -8370,7 +8265,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -8439,7 +8334,6 @@
           <t>Training or certificate</t>
         </is>
       </c>
-      <c r="AJ69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8497,7 +8391,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -8621,11 +8515,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -8677,13 +8567,11 @@
           <t>Detroit</t>
         </is>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8741,7 +8629,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -8872,7 +8760,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -9003,7 +8891,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -9134,7 +9022,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -9265,7 +9153,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -9396,7 +9284,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -9527,7 +9415,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -9596,7 +9484,6 @@
           <t>Training or certificate</t>
         </is>
       </c>
-      <c r="AJ78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9647,11 +9534,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>BeBee</t>
-        </is>
-      </c>
+      <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -9703,13 +9586,11 @@
           <t>Outside the area</t>
         </is>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9767,7 +9648,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -9898,7 +9779,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -10029,7 +9910,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -10160,7 +10041,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -10291,7 +10172,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -10422,7 +10303,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -10553,7 +10434,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -10684,7 +10565,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -10815,7 +10696,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -10946,7 +10827,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -11077,7 +10958,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -11201,11 +11082,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
+      <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -11257,13 +11134,11 @@
           <t>Detroit</t>
         </is>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11321,7 +11196,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -11452,7 +11327,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -11583,7 +11458,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -11714,7 +11589,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -11845,7 +11720,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -11976,7 +11851,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -12107,7 +11982,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -12238,7 +12113,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -12369,7 +12244,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -12500,7 +12375,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -12631,7 +12506,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -12762,7 +12637,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -12893,7 +12768,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -13017,11 +12892,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
+      <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -13073,13 +12944,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13137,7 +13006,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -13268,7 +13137,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -13392,11 +13261,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>Learn4Good</t>
-        </is>
-      </c>
+      <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -13448,13 +13313,11 @@
           <t>Outside the area</t>
         </is>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13512,7 +13375,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -13643,7 +13506,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -13774,7 +13637,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -13905,7 +13768,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -14036,7 +13899,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -14105,7 +13968,6 @@
           <t>Training or certificate</t>
         </is>
       </c>
-      <c r="AJ113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14163,7 +14025,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -14294,7 +14156,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -14418,11 +14280,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>Learn4Good</t>
-        </is>
-      </c>
+      <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -14474,13 +14332,11 @@
           <t>Outside the area</t>
         </is>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14538,7 +14394,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -14662,11 +14518,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
+      <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -14718,13 +14570,11 @@
           <t>Outside the area</t>
         </is>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14775,11 +14625,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>Edinburgh City FC</t>
-        </is>
-      </c>
+      <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -14831,13 +14677,11 @@
           <t>Southwest Detroit</t>
         </is>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14895,7 +14739,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -15026,7 +14870,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -15157,7 +15001,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -15226,7 +15070,6 @@
           <t>No degree required</t>
         </is>
       </c>
-      <c r="AJ122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15284,7 +15127,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -15408,11 +15251,7 @@
           <t>Full-time</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>ZipRecruiter</t>
-        </is>
-      </c>
+      <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -15464,13 +15303,11 @@
           <t>Outside the area</t>
         </is>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15528,7 +15365,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -15659,7 +15496,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -15783,11 +15620,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>Learn4Good</t>
-        </is>
-      </c>
+      <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -15839,13 +15672,11 @@
           <t>Outside the area</t>
         </is>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="AH127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15858,7 +15689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H509"/>
+  <dimension ref="A1:H524"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="2"/>
@@ -35167,6 +34998,431 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Remediation Department Manager - Environmental Services (Chicago | Detroit)</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>https://lensa.com/job-v1/burns-mcdonnell/detroit-mi/environmental-manager/8f13ad2615de24435e1007d67382340e?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Full-Time Executive Personal Assistant | Detroit, MI/ West Palm Beach, FL</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://www.estatejobs.com/job/u2xnt5/full-time-executive-personal-assistant-%7C-detroit-mi-west-palm-beach-fl/detroit/mi/united-states?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Strategic Purchasing Pro | Sourcing, Negotiation &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://bebee.com/us/jobs/strategic-purchasing-pro-sourcing-negotiation-supply-chain-flame-furnace-warren--lensa-7428_53581e415aef630e98203c088d3c8d92b74ce2385159589c4ba945c03a16ca0f?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Capex Portfolio Manager | Global Regional Lead</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://www.learn4good.com/jobs/detroit/michigan/management_and_managerial/5276952915/e/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Senior Controls Engineer | Detroit, MI</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/process-controls-engineer-detroit-mi/7331143?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer | Farmington Hills, MI</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/senior-mechanical-engineer-farmington-hills-mi/8265684?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer | Detroit, MI</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>https://www.sonara.ai/job-details/senior-electrical-engineer-at-imeg-consultants-d85bdf98-47a6-4ed9-0c86-cc65ee172fef?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>General Inquiry</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Impact Label Corporation</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>https://us.trabajo.org/job-4112-3ecfa63b765188c61166d570b28b1cb8?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Remote Solar Project Development Manager - Michigan</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Trajectory Energy</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>7 days ago</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>150K–180K a year</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>https://bebee.com/us/jobs/remote-solar-project-development-manager-michigan-trajectory-energy-michigan--jooble-8921159407354266833?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Security Officer I</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>DMC Huron Valley-Sinai Hospital</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Part-time</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>10 days ago</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>https://jobs.tenethealth.com/job/charter-township-of-commerce/security-officer-i/1127/97791436800?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Dispatcher – Central Dispatch | Ready Mix Concrete - Detroit, MI</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>https://careers-smyrnareadymix.icims.com/jobs/1946/dispatcher-%E2%80%93-central-dispatch-%7C-ready-mix-concrete---detroit%2C-mi/job?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Dispatcher - Central Dispatch | Ready Mix Concrete - Detroit, MI</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>https://www.nexxt.com/jobs/dispatcher-central-dispatch-ready-mix-concrete-detroit-mi-highland-park-mi-3289486137-job.html?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Full Time Non-Invasive Cardiologist Opportunity in Detroit, MI! Out-Patient Only! NO CALL / NO WEEKENDS! | J-1 &amp; H-1B Sponsorship</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>https://www.practicematch.com/physicians/jobs/cardiology/non-invasive-cardiology/michigan/detroit?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Certified Instrument Repair Technician | Onsite Gauging</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>https://talents.vaia.com/companies/daimler-truck-north-america/detroit/certified-instrument-repair-technician-onsite-gauging-76419674/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Senior Billing &amp; AR Specialist | QuickBooks &amp; Excel Master</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>https://talents.vaia.com/companies/marine-pollution-control/detroit/senior-billing-ar-specialist-quickbooks-excel-master-76395424/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
